--- a/data/UKPolling.xlsx
+++ b/data/UKPolling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="42">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -279,7 +279,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -472,7 +472,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1279"/>
+  <dimension ref="A1:F1405"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.63"/>
@@ -21878,10 +21878,10 @@
       </c>
     </row>
     <row r="1274" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1274" s="10" t="n">
+      <c r="A1274" s="8" t="n">
         <v>46001</v>
       </c>
-      <c r="B1274" s="0" t="n">
+      <c r="B1274" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C1274" s="9" t="s">
@@ -21895,10 +21895,10 @@
       </c>
     </row>
     <row r="1275" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1275" s="10" t="n">
+      <c r="A1275" s="8" t="n">
         <v>46001</v>
       </c>
-      <c r="B1275" s="0" t="n">
+      <c r="B1275" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C1275" s="9" t="s">
@@ -21907,15 +21907,15 @@
       <c r="D1275" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1275" s="0" t="n">
+      <c r="F1275" s="1" t="n">
         <v>2363</v>
       </c>
     </row>
     <row r="1276" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1276" s="10" t="n">
+      <c r="A1276" s="8" t="n">
         <v>46001</v>
       </c>
-      <c r="B1276" s="0" t="n">
+      <c r="B1276" s="1" t="n">
         <v>30</v>
       </c>
       <c r="C1276" s="9" t="s">
@@ -21924,15 +21924,15 @@
       <c r="D1276" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1276" s="0" t="n">
+      <c r="F1276" s="1" t="n">
         <v>2363</v>
       </c>
     </row>
     <row r="1277" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1277" s="10" t="n">
+      <c r="A1277" s="8" t="n">
         <v>46001</v>
       </c>
-      <c r="B1277" s="0" t="n">
+      <c r="B1277" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C1277" s="9" t="s">
@@ -21941,15 +21941,15 @@
       <c r="D1277" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1277" s="0" t="n">
+      <c r="F1277" s="1" t="n">
         <v>2363</v>
       </c>
     </row>
     <row r="1278" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1278" s="10" t="n">
+      <c r="A1278" s="8" t="n">
         <v>46001</v>
       </c>
-      <c r="B1278" s="0" t="n">
+      <c r="B1278" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C1278" s="9" t="s">
@@ -21958,15 +21958,15 @@
       <c r="D1278" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1278" s="0" t="n">
+      <c r="F1278" s="1" t="n">
         <v>2363</v>
       </c>
     </row>
     <row r="1279" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1279" s="10" t="n">
+      <c r="A1279" s="8" t="n">
         <v>46001</v>
       </c>
-      <c r="B1279" s="0" t="n">
+      <c r="B1279" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1279" s="9" t="s">
@@ -21975,8 +21975,2276 @@
       <c r="D1279" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1279" s="0" t="n">
+      <c r="F1279" s="1" t="n">
         <v>2363</v>
+      </c>
+    </row>
+    <row r="1280" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1280" s="8" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1280" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1280" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1280" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1280" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1280" s="1" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1281" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1281" s="8" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1281" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1281" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1281" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1281" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1281" s="1" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1282" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1282" s="8" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1282" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1282" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1282" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1282" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1282" s="1" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1283" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1283" s="8" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1283" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1283" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1283" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1283" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1283" s="1" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1284" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1284" s="8" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1284" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1284" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1284" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1284" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1284" s="1" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1285" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1285" s="8" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1285" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1285" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1285" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1285" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1285" s="1" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1286" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1286" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1286" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1286" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1286" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1286" s="1" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1287" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1287" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1287" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1287" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1287" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1287" s="1" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1288" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1288" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1288" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="C1288" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1288" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1288" s="1" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1289" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1289" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1289" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1289" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1289" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1289" s="1" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1290" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1290" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1290" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1290" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1290" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1290" s="1" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1291" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1291" s="8" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1291" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1291" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1291" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1291" s="1" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1292" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1292" s="8" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1292" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1292" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1292" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1292" s="1" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1293" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1293" s="8" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1293" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1293" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1293" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1293" s="1" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1294" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1294" s="8" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1294" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="C1294" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1294" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1294" s="1" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1295" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1295" s="8" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1295" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1295" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1295" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1295" s="1" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1296" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1296" s="8" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1296" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1296" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1296" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1296" s="1" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1297" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1297" s="8" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1297" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1297" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1297" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1297" s="1" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1298" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1298" s="8" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1298" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1298" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1298" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1298" s="1" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1299" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1299" s="8" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1299" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1299" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1299" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1299" s="1" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1300" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1300" s="8" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1300" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1300" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1300" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1300" s="1" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1301" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1301" s="8" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1301" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1301" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1301" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1301" s="1" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1302" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1302" s="8" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1302" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1302" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1302" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1302" s="1" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1303" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1303" s="8" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1303" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1303" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1303" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1303" s="1" t="n">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1304" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1304" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1304" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1304" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1304" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1304" s="1" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1305" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1305" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1305" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1305" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1305" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1305" s="1" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1306" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1306" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1306" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C1306" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1306" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1306" s="1" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1307" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1307" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1307" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1307" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1307" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1307" s="1" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1308" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1308" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1308" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1308" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1308" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1308" s="1" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1309" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1309" s="8" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1309" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1309" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1309" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1309" s="1" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1310" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1310" s="8" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1310" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1310" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1310" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1310" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1311" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1311" s="8" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1311" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1311" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1311" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1311" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1312" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1312" s="8" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1312" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="C1312" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1312" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1312" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1313" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1313" s="8" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1313" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1313" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1313" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1313" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1314" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1314" s="8" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1314" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1314" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1314" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1314" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1315" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1315" s="8" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1315" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1315" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1315" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1315" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1316" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1316" s="8" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1316" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1316" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1316" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1316" s="1" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1317" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1317" s="8" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1317" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1317" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1317" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1317" s="1" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1318" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1318" s="8" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1318" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1318" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1318" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1318" s="1" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1319" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1319" s="8" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1319" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1319" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1319" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1319" s="1" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1320" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1320" s="8" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1320" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1320" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1320" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1320" s="1" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1321" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1321" s="8" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1321" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1321" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1321" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1321" s="1" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1322" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1322" s="8" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1322" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1322" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1322" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1322" s="1" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1323" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1323" s="8" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1323" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1323" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1323" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1323" s="1" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1324" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1324" s="8" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1324" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1324" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1324" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1324" s="1" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1325" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1325" s="8" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1325" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1325" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1325" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1325" s="1" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1326" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1326" s="8" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1326" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1326" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1326" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1326" s="1" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1327" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1327" s="8" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1327" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1327" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1327" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1327" s="1" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1328" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1328" s="8" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B1328" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1328" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1328" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1328" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1329" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1329" s="8" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B1329" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C1329" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1329" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1329" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1330" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1330" s="8" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B1330" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1330" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1330" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1330" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1331" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1331" s="8" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B1331" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1331" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1331" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1331" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1332" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1332" s="8" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B1332" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1332" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1332" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1332" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1333" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1333" s="8" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B1333" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1333" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1333" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1333" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1334" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1334" s="8" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1334" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1334" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1334" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1334" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1334" s="1" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1335" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1335" s="8" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1335" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1335" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1335" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1335" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1335" s="1" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1336" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1336" s="8" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1336" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C1336" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1336" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1336" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1336" s="1" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1337" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1337" s="8" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1337" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1337" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1337" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1337" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1337" s="1" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1338" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1338" s="8" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1338" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1338" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1338" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1338" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1338" s="1" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1339" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1339" s="8" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1339" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1339" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1339" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1339" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1339" s="1" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="1340" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1340" s="8" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1340" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1340" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1340" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1340" s="1" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1341" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1341" s="8" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1341" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1341" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1341" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1341" s="1" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1342" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1342" s="8" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1342" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1342" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1342" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1342" s="1" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1343" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1343" s="8" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1343" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1343" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1343" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1343" s="1" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1344" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1344" s="8" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1344" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1344" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1344" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1344" s="1" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1345" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1345" s="8" t="n">
+        <v>-618712</v>
+      </c>
+      <c r="B1345" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1345" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1345" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1345" s="1" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1346" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1346" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1346" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1346" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1346" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1346" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1346" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1347" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1347" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1347" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1347" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1347" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1347" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1347" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1348" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1348" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1348" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1348" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1348" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1348" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1348" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1349" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1349" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1349" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1349" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1349" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1349" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1349" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1350" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1350" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1350" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1350" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1350" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1350" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1350" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1351" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1351" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1351" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1351" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1351" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1351" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1351" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1352" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1352" s="8" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1352" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1352" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1352" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1352" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1352" s="1" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1353" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1353" s="8" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1353" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1353" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1353" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1353" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1353" s="1" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1354" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1354" s="8" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1354" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1354" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1354" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1354" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1354" s="1" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1355" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1355" s="8" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1355" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1355" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1355" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1355" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1355" s="1" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1356" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1356" s="8" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1356" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1356" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1356" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1356" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1356" s="1" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1357" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1357" s="8" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1357" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1357" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1357" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1357" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1357" s="1" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="1358" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1358" s="8" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1358" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1358" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1358" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1358" s="1" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1359" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1359" s="8" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1359" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1359" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1359" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1359" s="1" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1360" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1360" s="8" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1360" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1360" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1360" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1360" s="1" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1361" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1361" s="8" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1361" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1361" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1361" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1361" s="1" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1362" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1362" s="8" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1362" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1362" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1362" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1362" s="1" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1363" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1363" s="8" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1363" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1363" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1363" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1363" s="1" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1364" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1364" s="8" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1364" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1364" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1364" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1364" s="1" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1365" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1365" s="8" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1365" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1365" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1365" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1365" s="1" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1366" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1366" s="8" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1366" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="C1366" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1366" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1366" s="1" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1367" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1367" s="8" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1367" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1367" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1367" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1367" s="1" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1368" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1368" s="8" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1368" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1368" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1368" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1368" s="1" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1369" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1369" s="8" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1369" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1369" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1369" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1369" s="1" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1370" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1370" s="8" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1370" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1370" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1370" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1370" s="1" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1371" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1371" s="8" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1371" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1371" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1371" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1371" s="1" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1372" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1372" s="8" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1372" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1372" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1372" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1372" s="1" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1373" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1373" s="8" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1373" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1373" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1373" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1373" s="1" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1374" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1374" s="8" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1374" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1374" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1374" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1374" s="1" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1375" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1375" s="8" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1375" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1375" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1375" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1375" s="1" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1376" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1376" s="8" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1376" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1376" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1376" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1376" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1376" s="1" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1377" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1377" s="8" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1377" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1377" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1377" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1377" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1377" s="1" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1378" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1378" s="8" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1378" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1378" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1378" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1378" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1378" s="1" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1379" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1379" s="8" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1379" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1379" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1379" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1379" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1379" s="1" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1380" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1380" s="8" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1380" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1380" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1380" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1380" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1380" s="1" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1381" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1381" s="8" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1381" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1381" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1381" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1381" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1381" s="1" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1382" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1382" s="8" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1382" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1382" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1382" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1382" s="1" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1383" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1383" s="8" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1383" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1383" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1383" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1383" s="1" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1384" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1384" s="8" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1384" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1384" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1384" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1384" s="1" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1385" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1385" s="8" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1385" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1385" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1385" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1385" s="1" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1386" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1386" s="8" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1386" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1386" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1386" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1386" s="1" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1387" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1387" s="8" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1387" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1387" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1387" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1387" s="1" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1388" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1388" s="8" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1388" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1388" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1388" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1388" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1388" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1389" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1389" s="8" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1389" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1389" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1389" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1389" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1389" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1390" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1390" s="8" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1390" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1390" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1390" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1390" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1390" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1391" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1391" s="8" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1391" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1391" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1391" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1391" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1391" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1392" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1392" s="8" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1392" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1392" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1392" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1392" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1392" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1393" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1393" s="8" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1393" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1393" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1393" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1393" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1393" s="1" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1394" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1394" s="8" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1394" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1394" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1394" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1394" s="10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1395" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1395" s="8" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1395" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1395" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1395" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1395" s="10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1396" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1396" s="8" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1396" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="C1396" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1396" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1396" s="10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1397" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1397" s="8" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1397" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1397" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1397" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1397" s="10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1398" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1398" s="8" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1398" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1398" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1398" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1398" s="10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1399" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1399" s="8" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1399" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1399" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1399" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1399" s="10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1400" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1400" s="8" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1400" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1400" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1400" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1400" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1400" s="10" t="n">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1401" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1401" s="8" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1401" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1401" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1401" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1401" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1401" s="10" t="n">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1402" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1402" s="8" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1402" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="C1402" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1402" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1402" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1402" s="10" t="n">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1403" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1403" s="8" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1403" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1403" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1403" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1403" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1403" s="10" t="n">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1404" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1404" s="8" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1404" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1404" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1404" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1404" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1404" s="10" t="n">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1405" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1405" s="8" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1405" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1405" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1405" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1405" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1405" s="10" t="n">
+        <v>2429</v>
       </c>
     </row>
   </sheetData>

--- a/data/UKPolling.xlsx
+++ b/data/UKPolling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="42">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -238,7 +238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -277,10 +277,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -472,7 +468,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1405"/>
+  <dimension ref="A1:F1423"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.63"/>
@@ -24029,7 +24025,7 @@
       <c r="A1394" s="8" t="n">
         <v>46047</v>
       </c>
-      <c r="B1394" s="10" t="n">
+      <c r="B1394" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C1394" s="9" t="s">
@@ -24038,7 +24034,7 @@
       <c r="D1394" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1394" s="10" t="n">
+      <c r="F1394" s="1" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -24046,7 +24042,7 @@
       <c r="A1395" s="8" t="n">
         <v>46047</v>
       </c>
-      <c r="B1395" s="10" t="n">
+      <c r="B1395" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C1395" s="9" t="s">
@@ -24055,7 +24051,7 @@
       <c r="D1395" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1395" s="10" t="n">
+      <c r="F1395" s="1" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -24063,7 +24059,7 @@
       <c r="A1396" s="8" t="n">
         <v>46047</v>
       </c>
-      <c r="B1396" s="10" t="n">
+      <c r="B1396" s="1" t="n">
         <v>29</v>
       </c>
       <c r="C1396" s="9" t="s">
@@ -24072,7 +24068,7 @@
       <c r="D1396" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1396" s="10" t="n">
+      <c r="F1396" s="1" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -24080,7 +24076,7 @@
       <c r="A1397" s="8" t="n">
         <v>46047</v>
       </c>
-      <c r="B1397" s="10" t="n">
+      <c r="B1397" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C1397" s="9" t="s">
@@ -24089,7 +24085,7 @@
       <c r="D1397" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1397" s="10" t="n">
+      <c r="F1397" s="1" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -24097,7 +24093,7 @@
       <c r="A1398" s="8" t="n">
         <v>46047</v>
       </c>
-      <c r="B1398" s="10" t="n">
+      <c r="B1398" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C1398" s="9" t="s">
@@ -24106,7 +24102,7 @@
       <c r="D1398" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1398" s="10" t="n">
+      <c r="F1398" s="1" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -24114,7 +24110,7 @@
       <c r="A1399" s="8" t="n">
         <v>46047</v>
       </c>
-      <c r="B1399" s="10" t="n">
+      <c r="B1399" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1399" s="9" t="s">
@@ -24123,7 +24119,7 @@
       <c r="D1399" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1399" s="10" t="n">
+      <c r="F1399" s="1" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -24131,7 +24127,7 @@
       <c r="A1400" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B1400" s="10" t="n">
+      <c r="B1400" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C1400" s="9" t="s">
@@ -24143,7 +24139,7 @@
       <c r="E1400" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1400" s="10" t="n">
+      <c r="F1400" s="1" t="n">
         <v>2429</v>
       </c>
     </row>
@@ -24151,7 +24147,7 @@
       <c r="A1401" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B1401" s="10" t="n">
+      <c r="B1401" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C1401" s="9" t="s">
@@ -24163,7 +24159,7 @@
       <c r="E1401" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1401" s="10" t="n">
+      <c r="F1401" s="1" t="n">
         <v>2429</v>
       </c>
     </row>
@@ -24171,7 +24167,7 @@
       <c r="A1402" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B1402" s="10" t="n">
+      <c r="B1402" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C1402" s="9" t="s">
@@ -24183,7 +24179,7 @@
       <c r="E1402" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1402" s="10" t="n">
+      <c r="F1402" s="1" t="n">
         <v>2429</v>
       </c>
     </row>
@@ -24191,7 +24187,7 @@
       <c r="A1403" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B1403" s="10" t="n">
+      <c r="B1403" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C1403" s="9" t="s">
@@ -24203,7 +24199,7 @@
       <c r="E1403" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1403" s="10" t="n">
+      <c r="F1403" s="1" t="n">
         <v>2429</v>
       </c>
     </row>
@@ -24211,7 +24207,7 @@
       <c r="A1404" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B1404" s="10" t="n">
+      <c r="B1404" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C1404" s="9" t="s">
@@ -24223,7 +24219,7 @@
       <c r="E1404" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1404" s="10" t="n">
+      <c r="F1404" s="1" t="n">
         <v>2429</v>
       </c>
     </row>
@@ -24231,7 +24227,7 @@
       <c r="A1405" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B1405" s="10" t="n">
+      <c r="B1405" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1405" s="9" t="s">
@@ -24243,8 +24239,332 @@
       <c r="E1405" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1405" s="10" t="n">
+      <c r="F1405" s="1" t="n">
         <v>2429</v>
+      </c>
+    </row>
+    <row r="1406" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1406" s="8" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1406" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1406" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1406" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1406" s="1" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1407" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1407" s="8" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1407" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1407" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1407" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1407" s="1" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1408" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1408" s="8" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1408" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1408" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1408" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1408" s="1" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1409" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1409" s="8" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1409" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1409" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1409" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1409" s="1" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1410" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1410" s="8" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1410" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1410" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1410" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1410" s="1" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1411" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1411" s="8" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1411" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1411" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1411" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1411" s="1" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1412" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1412" s="8" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1412" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1412" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1412" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1412" s="1" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1413" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1413" s="8" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1413" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1413" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1413" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1413" s="1" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1414" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1414" s="8" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1414" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="C1414" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1414" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1414" s="1" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1415" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1415" s="8" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1415" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1415" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1415" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1415" s="1" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1416" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1416" s="8" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1416" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1416" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1416" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1416" s="1" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1417" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1417" s="8" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1417" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1417" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1417" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1417" s="1" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1418" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1418" s="8" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1418" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1418" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1418" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1418" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1418" s="1" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1419" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1419" s="8" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1419" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1419" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1419" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1419" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1419" s="1" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1420" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1420" s="8" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1420" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1420" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1420" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1420" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1420" s="1" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1421" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1421" s="8" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1421" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1421" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1421" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1421" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1421" s="1" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1422" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1422" s="8" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1422" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1422" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1422" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1422" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1422" s="1" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1423" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1423" s="8" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1423" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1423" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1423" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1423" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1423" s="1" t="n">
+        <v>1513</v>
       </c>
     </row>
   </sheetData>

--- a/data/UKPolling.xlsx
+++ b/data/UKPolling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="42">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -238,7 +238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -277,6 +277,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -468,7 +472,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1423"/>
+  <dimension ref="A1:F1489"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.63"/>
@@ -24451,7 +24455,7 @@
       <c r="A1418" s="8" t="n">
         <v>46051</v>
       </c>
-      <c r="B1418" s="0" t="n">
+      <c r="B1418" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C1418" s="9" t="s">
@@ -24471,7 +24475,7 @@
       <c r="A1419" s="8" t="n">
         <v>46051</v>
       </c>
-      <c r="B1419" s="0" t="n">
+      <c r="B1419" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C1419" s="9" t="s">
@@ -24491,7 +24495,7 @@
       <c r="A1420" s="8" t="n">
         <v>46051</v>
       </c>
-      <c r="B1420" s="0" t="n">
+      <c r="B1420" s="1" t="n">
         <v>32</v>
       </c>
       <c r="C1420" s="9" t="s">
@@ -24511,7 +24515,7 @@
       <c r="A1421" s="8" t="n">
         <v>46051</v>
       </c>
-      <c r="B1421" s="0" t="n">
+      <c r="B1421" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C1421" s="9" t="s">
@@ -24531,7 +24535,7 @@
       <c r="A1422" s="8" t="n">
         <v>46051</v>
       </c>
-      <c r="B1422" s="0" t="n">
+      <c r="B1422" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C1422" s="9" t="s">
@@ -24551,7 +24555,7 @@
       <c r="A1423" s="8" t="n">
         <v>46051</v>
       </c>
-      <c r="B1423" s="0" t="n">
+      <c r="B1423" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1423" s="9" t="s">
@@ -24565,6 +24569,1200 @@
       </c>
       <c r="F1423" s="1" t="n">
         <v>1513</v>
+      </c>
+    </row>
+    <row r="1424" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1424" s="8" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1424" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1424" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1424" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1424" s="1" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1425" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1425" s="8" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1425" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1425" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1425" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1425" s="1" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1426" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1426" s="8" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1426" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1426" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1426" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1426" s="1" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1427" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1427" s="8" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1427" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1427" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1427" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1427" s="1" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1428" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1428" s="8" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1428" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1428" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1428" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1428" s="1" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1429" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1429" s="8" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1429" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1429" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1429" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1429" s="1" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1430" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1430" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1430" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1430" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1430" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1430" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1430" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1431" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1431" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1431" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1431" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1431" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1431" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1431" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1432" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1432" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1432" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1432" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1432" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1432" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1432" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1433" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1433" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1433" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1433" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1433" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1433" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1433" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1434" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1434" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1434" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1434" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1434" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1434" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1434" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1435" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1435" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1435" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1435" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1435" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1435" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1435" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1436" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1436" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1436" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1436" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1436" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1436" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1436" s="1" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1437" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1437" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1437" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1437" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1437" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1437" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1437" s="1" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1438" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1438" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1438" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C1438" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1438" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1438" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1438" s="1" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1439" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1439" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1439" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1439" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1439" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1439" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1439" s="1" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1440" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1440" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1440" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1440" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1440" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1440" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1440" s="1" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1441" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1441" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1441" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1441" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1441" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1441" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1441" s="1" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1442" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1442" s="8" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1442" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1442" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1442" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1442" s="1" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1443" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1443" s="8" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1443" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1443" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1443" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1443" s="1" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1444" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1444" s="8" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1444" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1444" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1444" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1444" s="1" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1445" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1445" s="8" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1445" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1445" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1445" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1445" s="1" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1446" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1446" s="8" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1446" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1446" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1446" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1446" s="1" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1447" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1447" s="8" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1447" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1447" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1447" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1447" s="1" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1448" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1448" s="8" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1448" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C1448" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1448" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1448" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1448" s="1" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1449" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1449" s="8" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1449" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1449" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1449" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1449" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1449" s="1" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1450" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1450" s="8" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1450" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1450" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1450" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1450" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1450" s="1" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1451" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1451" s="8" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1451" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1451" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1451" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1451" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1451" s="1" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1452" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1452" s="8" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1452" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1452" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1452" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1452" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1452" s="1" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1453" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1453" s="8" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1453" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1453" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1453" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1453" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1453" s="1" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1454" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1454" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B1454" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1454" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1454" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1454" s="0" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1455" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1455" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B1455" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1455" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1455" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1455" s="0" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1456" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1456" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B1456" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C1456" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1456" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1456" s="0" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1457" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1457" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B1457" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1457" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1457" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1457" s="0" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1458" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1458" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B1458" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1458" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1458" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1458" s="0" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1459" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1459" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B1459" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1459" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1459" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1459" s="0" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1460" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1460" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B1460" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C1460" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1460" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1460" s="0" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1461" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1461" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B1461" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1461" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1461" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1461" s="0" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1462" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1462" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B1462" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1462" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1462" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1462" s="0" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1463" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1463" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B1463" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1463" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1463" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1463" s="0" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1464" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1464" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B1464" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1464" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1464" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1464" s="0" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1465" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1465" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B1465" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1465" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1465" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1465" s="0" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1466" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1466" s="10" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B1466" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1466" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1466" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1466" s="0" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1467" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1467" s="10" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B1467" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1467" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1467" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1467" s="0" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1468" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1468" s="10" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B1468" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C1468" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1468" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1468" s="0" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1469" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1469" s="10" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B1469" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1469" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1469" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1469" s="0" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1470" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1470" s="10" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B1470" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1470" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1470" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1470" s="0" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1471" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1471" s="10" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B1471" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1471" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1471" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1471" s="0" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1472" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1472" s="10" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1472" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C1472" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1472" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1472" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1472" s="0" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1473" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1473" s="10" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1473" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1473" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1473" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1473" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1473" s="0" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1474" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1474" s="10" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1474" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1474" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1474" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1474" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1474" s="0" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1475" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1475" s="10" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1475" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1475" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1475" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1475" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1475" s="0" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1476" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1476" s="10" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1476" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1476" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1476" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1476" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1476" s="0" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1477" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1477" s="10" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1477" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1477" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1477" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1477" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1477" s="0" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1478" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1478" s="10" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B1478" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1478" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1478" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1478" s="0" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1479" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1479" s="10" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B1479" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1479" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1479" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1479" s="0" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1480" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1480" s="10" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B1480" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1480" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1480" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1480" s="0" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1481" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1481" s="10" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B1481" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1481" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1481" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1481" s="0" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1482" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1482" s="10" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B1482" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1482" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1482" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1482" s="0" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1483" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1483" s="10" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B1483" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1483" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1483" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1483" s="0" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1484" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1484" s="10" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B1484" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1484" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1484" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1484" s="0" t="n">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1485" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1485" s="10" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B1485" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1485" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1485" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1485" s="0" t="n">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1486" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1486" s="10" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B1486" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C1486" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1486" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1486" s="0" t="n">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1487" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1487" s="10" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B1487" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1487" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1487" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1487" s="0" t="n">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1488" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1488" s="10" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B1488" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1488" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1488" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1488" s="0" t="n">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1489" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1489" s="10" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B1489" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1489" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1489" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1489" s="0" t="n">
+        <v>2108</v>
       </c>
     </row>
   </sheetData>

--- a/data/UKPolling.xlsx
+++ b/data/UKPolling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3756" uniqueCount="42">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -279,8 +279,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -472,7 +472,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1489"/>
+  <dimension ref="A1:F1495"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.63"/>
@@ -25136,10 +25136,10 @@
       </c>
     </row>
     <row r="1454" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1454" s="10" t="n">
+      <c r="A1454" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="B1454" s="0" t="n">
+      <c r="B1454" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C1454" s="9" t="s">
@@ -25148,15 +25148,15 @@
       <c r="D1454" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1454" s="0" t="n">
+      <c r="F1454" s="1" t="n">
         <v>2466</v>
       </c>
     </row>
     <row r="1455" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1455" s="10" t="n">
+      <c r="A1455" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="B1455" s="0" t="n">
+      <c r="B1455" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C1455" s="9" t="s">
@@ -25165,15 +25165,15 @@
       <c r="D1455" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1455" s="0" t="n">
+      <c r="F1455" s="1" t="n">
         <v>2466</v>
       </c>
     </row>
     <row r="1456" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1456" s="10" t="n">
+      <c r="A1456" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="B1456" s="0" t="n">
+      <c r="B1456" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C1456" s="9" t="s">
@@ -25182,15 +25182,15 @@
       <c r="D1456" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1456" s="0" t="n">
+      <c r="F1456" s="1" t="n">
         <v>2466</v>
       </c>
     </row>
     <row r="1457" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1457" s="10" t="n">
+      <c r="A1457" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="B1457" s="0" t="n">
+      <c r="B1457" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C1457" s="9" t="s">
@@ -25199,15 +25199,15 @@
       <c r="D1457" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1457" s="0" t="n">
+      <c r="F1457" s="1" t="n">
         <v>2466</v>
       </c>
     </row>
     <row r="1458" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1458" s="10" t="n">
+      <c r="A1458" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="B1458" s="0" t="n">
+      <c r="B1458" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C1458" s="9" t="s">
@@ -25216,15 +25216,15 @@
       <c r="D1458" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1458" s="0" t="n">
+      <c r="F1458" s="1" t="n">
         <v>2466</v>
       </c>
     </row>
     <row r="1459" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1459" s="10" t="n">
+      <c r="A1459" s="8" t="n">
         <v>46062</v>
       </c>
-      <c r="B1459" s="0" t="n">
+      <c r="B1459" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1459" s="9" t="s">
@@ -25233,15 +25233,15 @@
       <c r="D1459" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1459" s="0" t="n">
+      <c r="F1459" s="1" t="n">
         <v>2466</v>
       </c>
     </row>
     <row r="1460" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1460" s="10" t="n">
+      <c r="A1460" s="8" t="n">
         <v>46063</v>
       </c>
-      <c r="B1460" s="0" t="n">
+      <c r="B1460" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C1460" s="9" t="s">
@@ -25250,15 +25250,15 @@
       <c r="D1460" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1460" s="0" t="n">
+      <c r="F1460" s="1" t="n">
         <v>2035</v>
       </c>
     </row>
     <row r="1461" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1461" s="10" t="n">
+      <c r="A1461" s="8" t="n">
         <v>46063</v>
       </c>
-      <c r="B1461" s="0" t="n">
+      <c r="B1461" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C1461" s="9" t="s">
@@ -25267,15 +25267,15 @@
       <c r="D1461" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1461" s="0" t="n">
+      <c r="F1461" s="1" t="n">
         <v>2035</v>
       </c>
     </row>
     <row r="1462" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1462" s="10" t="n">
+      <c r="A1462" s="8" t="n">
         <v>46063</v>
       </c>
-      <c r="B1462" s="0" t="n">
+      <c r="B1462" s="1" t="n">
         <v>30</v>
       </c>
       <c r="C1462" s="9" t="s">
@@ -25284,15 +25284,15 @@
       <c r="D1462" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1462" s="0" t="n">
+      <c r="F1462" s="1" t="n">
         <v>2035</v>
       </c>
     </row>
     <row r="1463" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1463" s="10" t="n">
+      <c r="A1463" s="8" t="n">
         <v>46063</v>
       </c>
-      <c r="B1463" s="0" t="n">
+      <c r="B1463" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C1463" s="9" t="s">
@@ -25301,15 +25301,15 @@
       <c r="D1463" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1463" s="0" t="n">
+      <c r="F1463" s="1" t="n">
         <v>2035</v>
       </c>
     </row>
     <row r="1464" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1464" s="10" t="n">
+      <c r="A1464" s="8" t="n">
         <v>46063</v>
       </c>
-      <c r="B1464" s="0" t="n">
+      <c r="B1464" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C1464" s="9" t="s">
@@ -25318,15 +25318,15 @@
       <c r="D1464" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1464" s="0" t="n">
+      <c r="F1464" s="1" t="n">
         <v>2035</v>
       </c>
     </row>
     <row r="1465" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1465" s="10" t="n">
+      <c r="A1465" s="8" t="n">
         <v>46063</v>
       </c>
-      <c r="B1465" s="0" t="n">
+      <c r="B1465" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C1465" s="9" t="s">
@@ -25335,15 +25335,15 @@
       <c r="D1465" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1465" s="0" t="n">
+      <c r="F1465" s="1" t="n">
         <v>2035</v>
       </c>
     </row>
     <row r="1466" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1466" s="10" t="n">
+      <c r="A1466" s="8" t="n">
         <v>46064</v>
       </c>
-      <c r="B1466" s="0" t="n">
+      <c r="B1466" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C1466" s="9" t="s">
@@ -25352,15 +25352,15 @@
       <c r="D1466" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1466" s="0" t="n">
+      <c r="F1466" s="1" t="n">
         <v>1394</v>
       </c>
     </row>
     <row r="1467" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1467" s="10" t="n">
+      <c r="A1467" s="8" t="n">
         <v>46064</v>
       </c>
-      <c r="B1467" s="0" t="n">
+      <c r="B1467" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C1467" s="9" t="s">
@@ -25369,15 +25369,15 @@
       <c r="D1467" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1467" s="0" t="n">
+      <c r="F1467" s="1" t="n">
         <v>1394</v>
       </c>
     </row>
     <row r="1468" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1468" s="10" t="n">
+      <c r="A1468" s="8" t="n">
         <v>46064</v>
       </c>
-      <c r="B1468" s="0" t="n">
+      <c r="B1468" s="1" t="n">
         <v>29</v>
       </c>
       <c r="C1468" s="9" t="s">
@@ -25386,15 +25386,15 @@
       <c r="D1468" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1468" s="0" t="n">
+      <c r="F1468" s="1" t="n">
         <v>1394</v>
       </c>
     </row>
     <row r="1469" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1469" s="10" t="n">
+      <c r="A1469" s="8" t="n">
         <v>46064</v>
       </c>
-      <c r="B1469" s="0" t="n">
+      <c r="B1469" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C1469" s="9" t="s">
@@ -25403,15 +25403,15 @@
       <c r="D1469" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1469" s="0" t="n">
+      <c r="F1469" s="1" t="n">
         <v>1394</v>
       </c>
     </row>
     <row r="1470" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1470" s="10" t="n">
+      <c r="A1470" s="8" t="n">
         <v>46064</v>
       </c>
-      <c r="B1470" s="0" t="n">
+      <c r="B1470" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C1470" s="9" t="s">
@@ -25420,15 +25420,15 @@
       <c r="D1470" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1470" s="0" t="n">
+      <c r="F1470" s="1" t="n">
         <v>1394</v>
       </c>
     </row>
     <row r="1471" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1471" s="10" t="n">
+      <c r="A1471" s="8" t="n">
         <v>46064</v>
       </c>
-      <c r="B1471" s="0" t="n">
+      <c r="B1471" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1471" s="9" t="s">
@@ -25437,15 +25437,15 @@
       <c r="D1471" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1471" s="0" t="n">
+      <c r="F1471" s="1" t="n">
         <v>1394</v>
       </c>
     </row>
     <row r="1472" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1472" s="10" t="n">
+      <c r="A1472" s="8" t="n">
         <v>46065</v>
       </c>
-      <c r="B1472" s="0" t="n">
+      <c r="B1472" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C1472" s="9" t="s">
@@ -25457,15 +25457,15 @@
       <c r="E1472" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1472" s="0" t="n">
+      <c r="F1472" s="1" t="n">
         <v>2006</v>
       </c>
     </row>
     <row r="1473" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1473" s="10" t="n">
+      <c r="A1473" s="8" t="n">
         <v>46065</v>
       </c>
-      <c r="B1473" s="0" t="n">
+      <c r="B1473" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C1473" s="9" t="s">
@@ -25477,15 +25477,15 @@
       <c r="E1473" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1473" s="0" t="n">
+      <c r="F1473" s="1" t="n">
         <v>2006</v>
       </c>
     </row>
     <row r="1474" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1474" s="10" t="n">
+      <c r="A1474" s="8" t="n">
         <v>46065</v>
       </c>
-      <c r="B1474" s="0" t="n">
+      <c r="B1474" s="1" t="n">
         <v>31</v>
       </c>
       <c r="C1474" s="9" t="s">
@@ -25497,15 +25497,15 @@
       <c r="E1474" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1474" s="0" t="n">
+      <c r="F1474" s="1" t="n">
         <v>2006</v>
       </c>
     </row>
     <row r="1475" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1475" s="10" t="n">
+      <c r="A1475" s="8" t="n">
         <v>46065</v>
       </c>
-      <c r="B1475" s="0" t="n">
+      <c r="B1475" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C1475" s="9" t="s">
@@ -25517,15 +25517,15 @@
       <c r="E1475" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1475" s="0" t="n">
+      <c r="F1475" s="1" t="n">
         <v>2006</v>
       </c>
     </row>
     <row r="1476" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1476" s="10" t="n">
+      <c r="A1476" s="8" t="n">
         <v>46065</v>
       </c>
-      <c r="B1476" s="0" t="n">
+      <c r="B1476" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C1476" s="9" t="s">
@@ -25537,15 +25537,15 @@
       <c r="E1476" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1476" s="0" t="n">
+      <c r="F1476" s="1" t="n">
         <v>2006</v>
       </c>
     </row>
     <row r="1477" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1477" s="10" t="n">
+      <c r="A1477" s="8" t="n">
         <v>46065</v>
       </c>
-      <c r="B1477" s="0" t="n">
+      <c r="B1477" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C1477" s="9" t="s">
@@ -25557,15 +25557,15 @@
       <c r="E1477" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1477" s="0" t="n">
+      <c r="F1477" s="1" t="n">
         <v>2006</v>
       </c>
     </row>
     <row r="1478" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1478" s="10" t="n">
+      <c r="A1478" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="B1478" s="0" t="n">
+      <c r="B1478" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C1478" s="9" t="s">
@@ -25574,15 +25574,15 @@
       <c r="D1478" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1478" s="0" t="n">
+      <c r="F1478" s="1" t="n">
         <v>2384</v>
       </c>
     </row>
     <row r="1479" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1479" s="10" t="n">
+      <c r="A1479" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="B1479" s="0" t="n">
+      <c r="B1479" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C1479" s="9" t="s">
@@ -25591,15 +25591,15 @@
       <c r="D1479" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1479" s="0" t="n">
+      <c r="F1479" s="1" t="n">
         <v>2384</v>
       </c>
     </row>
     <row r="1480" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1480" s="10" t="n">
+      <c r="A1480" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="B1480" s="0" t="n">
+      <c r="B1480" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C1480" s="9" t="s">
@@ -25608,15 +25608,15 @@
       <c r="D1480" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1480" s="0" t="n">
+      <c r="F1480" s="1" t="n">
         <v>2384</v>
       </c>
     </row>
     <row r="1481" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1481" s="10" t="n">
+      <c r="A1481" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="B1481" s="0" t="n">
+      <c r="B1481" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C1481" s="9" t="s">
@@ -25625,15 +25625,15 @@
       <c r="D1481" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1481" s="0" t="n">
+      <c r="F1481" s="1" t="n">
         <v>2384</v>
       </c>
     </row>
     <row r="1482" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1482" s="10" t="n">
+      <c r="A1482" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="B1482" s="0" t="n">
+      <c r="B1482" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C1482" s="9" t="s">
@@ -25642,15 +25642,15 @@
       <c r="D1482" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1482" s="0" t="n">
+      <c r="F1482" s="1" t="n">
         <v>2384</v>
       </c>
     </row>
     <row r="1483" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1483" s="10" t="n">
+      <c r="A1483" s="8" t="n">
         <v>46069</v>
       </c>
-      <c r="B1483" s="0" t="n">
+      <c r="B1483" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C1483" s="9" t="s">
@@ -25659,15 +25659,15 @@
       <c r="D1483" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1483" s="0" t="n">
+      <c r="F1483" s="1" t="n">
         <v>2384</v>
       </c>
     </row>
     <row r="1484" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1484" s="10" t="n">
+      <c r="A1484" s="8" t="n">
         <v>46070</v>
       </c>
-      <c r="B1484" s="0" t="n">
+      <c r="B1484" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C1484" s="9" t="s">
@@ -25676,15 +25676,15 @@
       <c r="D1484" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1484" s="0" t="n">
+      <c r="F1484" s="1" t="n">
         <v>2108</v>
       </c>
     </row>
     <row r="1485" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1485" s="10" t="n">
+      <c r="A1485" s="8" t="n">
         <v>46070</v>
       </c>
-      <c r="B1485" s="0" t="n">
+      <c r="B1485" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C1485" s="9" t="s">
@@ -25693,15 +25693,15 @@
       <c r="D1485" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1485" s="0" t="n">
+      <c r="F1485" s="1" t="n">
         <v>2108</v>
       </c>
     </row>
     <row r="1486" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1486" s="10" t="n">
+      <c r="A1486" s="8" t="n">
         <v>46070</v>
       </c>
-      <c r="B1486" s="0" t="n">
+      <c r="B1486" s="1" t="n">
         <v>28</v>
       </c>
       <c r="C1486" s="9" t="s">
@@ -25710,15 +25710,15 @@
       <c r="D1486" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1486" s="0" t="n">
+      <c r="F1486" s="1" t="n">
         <v>2108</v>
       </c>
     </row>
     <row r="1487" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1487" s="10" t="n">
+      <c r="A1487" s="8" t="n">
         <v>46070</v>
       </c>
-      <c r="B1487" s="0" t="n">
+      <c r="B1487" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C1487" s="9" t="s">
@@ -25727,15 +25727,15 @@
       <c r="D1487" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1487" s="0" t="n">
+      <c r="F1487" s="1" t="n">
         <v>2108</v>
       </c>
     </row>
     <row r="1488" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1488" s="10" t="n">
+      <c r="A1488" s="8" t="n">
         <v>46070</v>
       </c>
-      <c r="B1488" s="0" t="n">
+      <c r="B1488" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C1488" s="9" t="s">
@@ -25744,15 +25744,15 @@
       <c r="D1488" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1488" s="0" t="n">
+      <c r="F1488" s="1" t="n">
         <v>2108</v>
       </c>
     </row>
     <row r="1489" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1489" s="10" t="n">
+      <c r="A1489" s="8" t="n">
         <v>46070</v>
       </c>
-      <c r="B1489" s="0" t="n">
+      <c r="B1489" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C1489" s="9" t="s">
@@ -25761,8 +25761,110 @@
       <c r="D1489" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1489" s="0" t="n">
+      <c r="F1489" s="1" t="n">
         <v>2108</v>
+      </c>
+    </row>
+    <row r="1490" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1490" s="10" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1490" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1490" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1490" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1490" s="0" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="1491" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1491" s="10" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1491" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1491" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1491" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1491" s="0" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="1492" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1492" s="10" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1492" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C1492" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1492" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1492" s="0" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="1493" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1493" s="10" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1493" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1493" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1493" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1493" s="0" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="1494" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1494" s="10" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1494" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1494" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1494" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1494" s="0" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="1495" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1495" s="10" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1495" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1495" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1495" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1495" s="0" t="n">
+        <v>2178</v>
       </c>
     </row>
   </sheetData>

--- a/data/UKPolling.xlsx
+++ b/data/UKPolling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3792" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3834" uniqueCount="43">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -241,7 +241,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -288,6 +288,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -479,7 +483,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1513"/>
+  <dimension ref="A1:F1531"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.63"/>
@@ -25978,25 +25982,25 @@
       </c>
     </row>
     <row r="1502" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1502" s="10" t="n">
-        <v>46073</v>
+      <c r="A1502" s="12" t="n">
+        <v>46072</v>
       </c>
       <c r="B1502" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C1502" s="11" t="s">
         <v>6</v>
       </c>
       <c r="D1502" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F1502" s="2" t="n">
-        <v>2015</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="1503" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1503" s="10" t="n">
-        <v>46073</v>
+      <c r="A1503" s="12" t="n">
+        <v>46072</v>
       </c>
       <c r="B1503" s="2" t="n">
         <v>20</v>
@@ -26005,134 +26009,134 @@
         <v>8</v>
       </c>
       <c r="D1503" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F1503" s="2" t="n">
-        <v>2015</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="1504" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1504" s="10" t="n">
-        <v>46073</v>
+      <c r="A1504" s="12" t="n">
+        <v>46072</v>
       </c>
       <c r="B1504" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C1504" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D1504" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F1504" s="2" t="n">
-        <v>2015</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="1505" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1505" s="10" t="n">
-        <v>46073</v>
+      <c r="A1505" s="12" t="n">
+        <v>46072</v>
       </c>
       <c r="B1505" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C1505" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D1505" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F1505" s="2" t="n">
-        <v>2015</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="1506" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1506" s="10" t="n">
-        <v>46073</v>
+      <c r="A1506" s="12" t="n">
+        <v>46072</v>
       </c>
       <c r="B1506" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C1506" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D1506" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F1506" s="2" t="n">
-        <v>2015</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="1507" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1507" s="10" t="n">
-        <v>46073</v>
+      <c r="A1507" s="12" t="n">
+        <v>46072</v>
       </c>
       <c r="B1507" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1507" s="11" t="s">
         <v>12</v>
       </c>
       <c r="D1507" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F1507" s="2" t="n">
-        <v>2015</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="1508" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1508" s="10" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="B1508" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C1508" s="11" t="s">
         <v>6</v>
       </c>
       <c r="D1508" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F1508" s="2" t="n">
-        <v>2043</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1509" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1509" s="10" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="B1509" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1509" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D1509" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F1509" s="2" t="n">
-        <v>2043</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1510" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1510" s="10" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="B1510" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1510" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D1510" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F1510" s="2" t="n">
-        <v>2043</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1511" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1511" s="10" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="B1511" s="2" t="n">
         <v>14</v>
@@ -26141,44 +26145,368 @@
         <v>10</v>
       </c>
       <c r="D1511" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F1511" s="2" t="n">
-        <v>2043</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1512" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1512" s="10" t="n">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="B1512" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C1512" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D1512" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F1512" s="2" t="n">
-        <v>2043</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1513" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1513" s="10" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B1513" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1513" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1513" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1513" s="2" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="1514" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1514" s="10" t="n">
         <v>46076</v>
       </c>
-      <c r="B1513" s="2" t="n">
+      <c r="B1514" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1514" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1514" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1514" s="2" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1515" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1515" s="10" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1515" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1515" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1515" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1515" s="2" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1516" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1516" s="10" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1516" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1516" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1516" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1516" s="2" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1517" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1517" s="10" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1517" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1517" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1517" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1517" s="2" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1518" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1518" s="10" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1518" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1518" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1518" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1518" s="2" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1519" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1519" s="10" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1519" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C1513" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1513" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1513" s="2" t="n">
+      <c r="C1519" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1519" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1519" s="2" t="n">
         <v>2043</v>
+      </c>
+    </row>
+    <row r="1520" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1520" s="12" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1520" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1520" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1520" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1520" s="0" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1521" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1521" s="12" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1521" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1521" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1521" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1521" s="0" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1522" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1522" s="12" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1522" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C1522" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1522" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1522" s="0" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1523" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1523" s="12" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1523" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1523" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1523" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1523" s="0" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1524" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1524" s="12" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1524" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1524" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1524" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1524" s="0" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1525" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1525" s="12" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1525" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1525" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1525" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1525" s="0" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1526" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1526" s="12" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1526" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1526" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1526" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1526" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1526" s="0" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1527" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1527" s="12" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1527" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1527" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1527" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1527" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1527" s="0" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1528" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1528" s="12" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1528" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1528" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1528" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1528" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1528" s="0" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1529" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1529" s="12" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1529" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1529" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1529" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1529" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1529" s="0" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1530" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1530" s="12" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1530" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1530" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1530" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1530" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1530" s="0" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1531" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1531" s="12" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1531" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1531" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1531" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1531" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1531" s="0" t="n">
+        <v>2050</v>
       </c>
     </row>
   </sheetData>
